--- a/config/generated/templates/LightConeSuperimposition.xlsx
+++ b/config/generated/templates/LightConeSuperimposition.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>@table</t>
   </si>
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>a6c3aac4cba69b90</t>
+    <t>7de404130267dbfb</t>
   </si>
   <si>
     <t>#name</t>
@@ -61,6 +61,9 @@
     <t>constant_across_ranks</t>
   </si>
   <si>
+    <t>modifier_identity_ids</t>
+  </si>
+  <si>
     <t>#field</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>optional&lt;list&lt;ref&lt;ContentIdentity.id&gt;&gt;&gt;</t>
+  </si>
+  <si>
     <t>#scope</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
   </si>
   <si>
     <t>length=1..32</t>
+  </si>
+  <si>
+    <t>parser=split;separator=|;length=0..32</t>
   </si>
   <si>
     <t>#desc</t>
@@ -520,6 +529,7 @@
     <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="21.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -571,10 +581,13 @@
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -590,31 +603,37 @@
       </c>
       <c r="F3" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -629,34 +648,41 @@
         <v>6</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/config/generated/templates/LightConeSuperimposition.xlsx
+++ b/config/generated/templates/LightConeSuperimposition.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>7de404130267dbfb</t>
+    <t>e9f87ef0e6b3cb27</t>
   </si>
   <si>
     <t>#name</t>
@@ -85,7 +85,7 @@
     <t>optional&lt;list&lt;ref&lt;ContentIdentity.id&gt;&gt;&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
